--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -94,142 +94,142 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>Team Alpha</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
     <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>Team Alpha</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
   </si>
   <si>
     <t>Team Lambda</t>
@@ -1165,10 +1165,10 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -1176,13 +1176,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -1190,13 +1190,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -1204,13 +1204,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -1218,10 +1218,10 @@
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -1229,83 +1229,83 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
         <v>65</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -1322,12 +1322,12 @@
         <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
         <v>67</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
         <v>70</v>

--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -94,6 +94,204 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -101,204 +299,6 @@
   </si>
   <si>
     <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1224,194 +1224,194 @@
         <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
         <v>86</v>

--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>Number of pools</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Hermione Granger</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -121,6 +133,9 @@
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
@@ -130,6 +145,9 @@
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Pool B</t>
   </si>
   <si>
@@ -142,6 +160,9 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Jon Snow</t>
   </si>
   <si>
@@ -151,6 +172,9 @@
     <t>SNOW</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
@@ -160,6 +184,9 @@
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
@@ -169,6 +196,9 @@
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
@@ -178,6 +208,9 @@
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Pool C</t>
   </si>
   <si>
@@ -190,6 +223,9 @@
     <t>STARK</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
@@ -199,6 +235,9 @@
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
@@ -208,6 +247,9 @@
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -217,6 +259,9 @@
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Pool D</t>
   </si>
   <si>
@@ -229,6 +274,9 @@
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Inigo Montoya</t>
   </si>
   <si>
@@ -238,12 +286,18 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
@@ -253,6 +307,9 @@
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
@@ -262,6 +319,9 @@
     <t>WONKA</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Pool E</t>
   </si>
   <si>
@@ -274,9 +334,15 @@
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Team Lambda</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
@@ -286,12 +352,18 @@
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
     <t>Team Upsilon</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -301,6 +373,9 @@
     <t>YGRITTE</t>
   </si>
   <si>
+    <t>K24</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -353,78 +428,6 @@
   </si>
   <si>
     <t>5.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>E5</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -1086,341 +1089,416 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>70</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>99</v>
+      </c>
+      <c r="E22" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>105</v>
+      </c>
+      <c r="E24" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1438,112 +1516,112 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>107</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>108</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>109</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>110</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>111</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>112</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>113</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>114</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>115</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>116</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>117</v>
+      <c r="A11" s="28" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B11" s="29" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>118</v>
+      <c r="A12" s="28" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="29" t="str">
         <f>'data'!D14</f>
       </c>
     </row>
     <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="28" t="s">
-        <v>119</v>
+      <c r="A13" s="28" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B13" s="29" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="28" t="s">
-        <v>120</v>
+      <c r="A14" s="28" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B14" s="29" t="str">
         <f>'data'!D16</f>
@@ -1572,80 +1650,80 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>121</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>122</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>123</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>124</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>125</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>126</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>127</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>128</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>129</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>130</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D26</f>
@@ -1673,242 +1751,242 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
-        <v>117</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2145,7 +2223,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -2156,7 +2234,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -2166,7 +2244,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -2176,7 +2254,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -2186,7 +2264,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -2196,7 +2274,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -2206,7 +2284,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -2279,54 +2357,54 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="D6" s="12" t="str">
-        <f>"1. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D7" s="12" t="str">
-        <f>"2. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="D8" s="12" t="str">
-        <f>"3. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="12" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D9" s="12" t="str">
-        <f>"4. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="F9" s="12" t="str">
-        <f>"4. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="12" t="str">
-        <f>"5. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="F10" s="12" t="str">
-        <f>"5. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="12">
@@ -2339,44 +2417,44 @@
         <f>'data'!$A$12</f>
       </c>
       <c r="D13" s="12" t="str">
-        <f>"1. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="12" t="str">
-        <f>"1. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="D14" s="12" t="str">
-        <f>"2. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="12" t="str">
-        <f>"2. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="D15" s="12" t="str">
-        <f>"3. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="12" t="str">
-        <f>"3. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="D16" s="12" t="str">
-        <f>"4. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="12" t="str">
-        <f>"4. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="D17" s="12" t="str">
-        <f>"5. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="12" t="str">
-        <f>"5. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
     </row>
   </sheetData>
@@ -2411,7 +2489,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2420,7 +2498,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -2451,27 +2529,27 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2479,10 +2557,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -2490,12 +2568,12 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2503,10 +2581,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="I5" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2514,12 +2592,12 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2527,10 +2605,10 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="I6" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -2538,12 +2616,12 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -2551,10 +2629,10 @@
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="G7" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="I7" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -2562,12 +2640,12 @@
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
       <c r="O7" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -2575,10 +2653,10 @@
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="I8" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J8" s="18"/>
       <c r="K8" s="18"/>
@@ -2586,56 +2664,56 @@
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
       <c r="O8" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B11" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),IF(OR(D8="X",D8="x",AND(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))*1),0)</f>
@@ -2656,7 +2734,7 @@
         <f>RANK(U11,$U$11:$U$15)+COUNTIF($U$10:U10,U11)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J11" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J8,K8,M8,N8)&gt;0,OR(L8="X",L8="x")),IF(OR(L8="X",L8="x",AND(OR(COUNTA(J8,K8,M8,N8)&gt;0,OR(L8="X",L8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-","")))*1),0)</f>
@@ -2685,7 +2763,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B12" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2706,7 +2784,7 @@
         <f>RANK(U12,$U$11:$U$15)+COUNTIF($U$10:U11,U12)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="J12" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2735,7 +2813,7 @@
     </row>
     <row r="13">
       <c r="A13" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B13" s="14" t="str">
         <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2756,7 +2834,7 @@
         <f>RANK(U13,$U$11:$U$15)+COUNTIF($U$10:U12,U13)</f>
       </c>
       <c r="I13" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="J13" s="14" t="str">
         <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2785,7 +2863,7 @@
     </row>
     <row r="14">
       <c r="A14" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B14" s="14" t="str">
         <f>IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),IF(OR(D7="X",D7="x",AND(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))*1),0)</f>
@@ -2806,7 +2884,7 @@
         <f>RANK(U14,$U$11:$U$15)+COUNTIF($U$10:U13,U14)</f>
       </c>
       <c r="I14" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J14" s="14" t="str">
         <f>IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J7,K7,M7,N7)&gt;0,OR(L7="X",L7="x")),IF(OR(L7="X",L7="x",AND(OR(COUNTA(J7,K7,M7,N7)&gt;0,OR(L7="X",L7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-","")))*1),0)</f>
@@ -2835,7 +2913,7 @@
     </row>
     <row r="15">
       <c r="A15" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B15" s="14" t="str">
         <f>IF(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),IF(OR(D7="X",D7="x",AND(OR(COUNTA(B7,C7,E7,F7)&gt;0,OR(D7="X",D7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),IF(OR(D8="X",D8="x",AND(OR(COUNTA(B8,C8,E8,F8)&gt;0,OR(D8="X",D8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))*1),0)</f>
@@ -2856,7 +2934,7 @@
         <f>RANK(U15,$U$11:$U$15)+COUNTIF($U$10:U14,U15)</f>
       </c>
       <c r="I15" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
       <c r="J15" s="14" t="str">
         <f>IF(OR(COUNTA(J7,K7,M7,N7)&gt;0,OR(L7="X",L7="x")),IF(OR(L7="X",L7="x",AND(OR(COUNTA(J7,K7,M7,N7)&gt;0,OR(L7="X",L7="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N7," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K7," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J8,K8,M8,N8)&gt;0,OR(L8="X",L8="x")),IF(OR(L8="X",L8="x",AND(OR(COUNTA(J8,K8,M8,N8)&gt;0,OR(L8="X",L8="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N8," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K8," ",""),"0",""),"-","")))*1),0)</f>
@@ -2886,22 +2964,22 @@
     <row r="18">
       <c r="F18" s="13"/>
       <c r="G18" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="F19" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G19" s="19" t="str">
         <f>IFERROR(INDEX($A$11:$A$15, MATCH(1, $G$11:$G$15, 0)), "-")</f>
       </c>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O19" s="19" t="str">
         <f>IFERROR(INDEX($I$11:$I$15, MATCH(1, $O$11:$O$15, 0)), "-")</f>
@@ -2909,13 +2987,13 @@
     </row>
     <row r="20">
       <c r="F20" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G20" s="19" t="str">
         <f>IFERROR(INDEX($A$11:$A$15, MATCH(2, $G$11:$G$15, 0)), "-")</f>
       </c>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="O20" s="19" t="str">
         <f>IFERROR(INDEX($I$11:$I$15, MATCH(2, $O$11:$O$15, 0)), "-")</f>
@@ -2923,13 +3001,13 @@
     </row>
     <row r="21">
       <c r="F21" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="G21" s="19" t="str">
         <f>IFERROR(INDEX($A$11:$A$15, MATCH(3, $G$11:$G$15, 0)), "-")</f>
       </c>
       <c r="N21" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="O21" s="19" t="str">
         <f>IFERROR(INDEX($I$11:$I$15, MATCH(3, $O$11:$O$15, 0)), "-")</f>
@@ -2937,13 +3015,13 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G22" s="19" t="str">
         <f>IFERROR(INDEX($A$11:$A$15, MATCH(4, $G$11:$G$15, 0)), "-")</f>
       </c>
       <c r="N22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O22" s="19" t="str">
         <f>IFERROR(INDEX($I$11:$I$15, MATCH(4, $O$11:$O$15, 0)), "-")</f>
@@ -2951,13 +3029,13 @@
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G23" s="19" t="str">
         <f>IFERROR(INDEX($A$11:$A$15, MATCH(5, $G$11:$G$15, 0)), "-")</f>
       </c>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O23" s="19" t="str">
         <f>IFERROR(INDEX($I$11:$I$15, MATCH(5, $O$11:$O$15, 0)), "-")</f>
@@ -2985,27 +3063,27 @@
     </row>
     <row r="26">
       <c r="A26" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="O26" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -3013,10 +3091,10 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
@@ -3024,12 +3102,12 @@
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -3037,10 +3115,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -3048,12 +3126,12 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -3061,10 +3139,10 @@
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="I29" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
@@ -3072,12 +3150,12 @@
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
@@ -3085,10 +3163,10 @@
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I30" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
@@ -3096,12 +3174,12 @@
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -3109,10 +3187,10 @@
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I31" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
@@ -3120,56 +3198,56 @@
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B34" s="14" t="str">
         <f>IF(OR(COUNTA(B27,C27,E27,F27)&gt;0,OR(D27="X",D27="x")),IF(OR(D27="X",D27="x",AND(OR(COUNTA(B27,C27,E27,F27)&gt;0,OR(D27="X",D27="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B31,C31,E31,F31)&gt;0,OR(D31="X",D31="x")),IF(OR(D31="X",D31="x",AND(OR(COUNTA(B31,C31,E31,F31)&gt;0,OR(D31="X",D31="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-","")))*1),0)</f>
@@ -3190,7 +3268,7 @@
         <f>RANK(U34,$U$34:$U$38)+COUNTIF($U$33:U33,U34)</f>
       </c>
       <c r="I34" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J34" s="14" t="str">
         <f>IF(OR(COUNTA(J27,K27,M27,N27)&gt;0,OR(L27="X",L27="x")),IF(OR(L27="X",L27="x",AND(OR(COUNTA(J27,K27,M27,N27)&gt;0,OR(L27="X",L27="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J31,K31,M31,N31)&gt;0,OR(L31="X",L31="x")),IF(OR(L31="X",L31="x",AND(OR(COUNTA(J31,K31,M31,N31)&gt;0,OR(L31="X",L31="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N31," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K31," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N31," ",""),"0",""),"-","")))*1),0)</f>
@@ -3219,7 +3297,7 @@
     </row>
     <row r="35">
       <c r="A35" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B35" s="14" t="str">
         <f>IF(OR(COUNTA(B27,C27,E27,F27)&gt;0,OR(D27="X",D27="x")),IF(OR(D27="X",D27="x",AND(OR(COUNTA(B27,C27,E27,F27)&gt;0,OR(D27="X",D27="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C27," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F27," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B28,C28,E28,F28)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x",AND(OR(COUNTA(B28,C28,E28,F28)&gt;0,OR(D28="X",D28="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-","")))*1),0)</f>
@@ -3240,7 +3318,7 @@
         <f>RANK(U35,$U$34:$U$38)+COUNTIF($U$33:U34,U35)</f>
       </c>
       <c r="I35" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J35" s="14" t="str">
         <f>IF(OR(COUNTA(J27,K27,M27,N27)&gt;0,OR(L27="X",L27="x")),IF(OR(L27="X",L27="x",AND(OR(COUNTA(J27,K27,M27,N27)&gt;0,OR(L27="X",L27="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K27," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M27," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N27," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J28,K28,M28,N28)&gt;0,OR(L28="X",L28="x")),IF(OR(L28="X",L28="x",AND(OR(COUNTA(J28,K28,M28,N28)&gt;0,OR(L28="X",L28="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-","")))*1),0)</f>
@@ -3269,7 +3347,7 @@
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B36" s="14" t="str">
         <f>IF(OR(COUNTA(B28,C28,E28,F28)&gt;0,OR(D28="X",D28="x")),IF(OR(D28="X",D28="x",AND(OR(COUNTA(B28,C28,E28,F28)&gt;0,OR(D28="X",D28="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F28," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C28," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B29,C29,E29,F29)&gt;0,OR(D29="X",D29="x")),IF(OR(D29="X",D29="x",AND(OR(COUNTA(B29,C29,E29,F29)&gt;0,OR(D29="X",D29="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))*1),0)</f>
@@ -3290,7 +3368,7 @@
         <f>RANK(U36,$U$34:$U$38)+COUNTIF($U$33:U35,U36)</f>
       </c>
       <c r="I36" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
       <c r="J36" s="14" t="str">
         <f>IF(OR(COUNTA(J28,K28,M28,N28)&gt;0,OR(L28="X",L28="x")),IF(OR(L28="X",L28="x",AND(OR(COUNTA(J28,K28,M28,N28)&gt;0,OR(L28="X",L28="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N28," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J28," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K28," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J29,K29,M29,N29)&gt;0,OR(L29="X",L29="x")),IF(OR(L29="X",L29="x",AND(OR(COUNTA(J29,K29,M29,N29)&gt;0,OR(L29="X",L29="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")))*1),0)</f>
@@ -3319,7 +3397,7 @@
     </row>
     <row r="37">
       <c r="A37" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B37" s="14" t="str">
         <f>IF(OR(COUNTA(B29,C29,E29,F29)&gt;0,OR(D29="X",D29="x")),IF(OR(D29="X",D29="x",AND(OR(COUNTA(B29,C29,E29,F29)&gt;0,OR(D29="X",D29="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C29," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F29," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B30,C30,E30,F30)&gt;0,OR(D30="X",D30="x")),IF(OR(D30="X",D30="x",AND(OR(COUNTA(B30,C30,E30,F30)&gt;0,OR(D30="X",D30="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-","")))*1),0)</f>
@@ -3340,7 +3418,7 @@
         <f>RANK(U37,$U$34:$U$38)+COUNTIF($U$33:U36,U37)</f>
       </c>
       <c r="I37" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J37" s="14" t="str">
         <f>IF(OR(COUNTA(J29,K29,M29,N29)&gt;0,OR(L29="X",L29="x")),IF(OR(L29="X",L29="x",AND(OR(COUNTA(J29,K29,M29,N29)&gt;0,OR(L29="X",L29="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K29," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M29," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N29," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J30,K30,M30,N30)&gt;0,OR(L30="X",L30="x")),IF(OR(L30="X",L30="x",AND(OR(COUNTA(J30,K30,M30,N30)&gt;0,OR(L30="X",L30="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-","")))*1),0)</f>
@@ -3369,7 +3447,7 @@
     </row>
     <row r="38">
       <c r="A38" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="B38" s="14" t="str">
         <f>IF(OR(COUNTA(B30,C30,E30,F30)&gt;0,OR(D30="X",D30="x")),IF(OR(D30="X",D30="x",AND(OR(COUNTA(B30,C30,E30,F30)&gt;0,OR(D30="X",D30="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F30," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C30," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B31,C31,E31,F31)&gt;0,OR(D31="X",D31="x")),IF(OR(D31="X",D31="x",AND(OR(COUNTA(B31,C31,E31,F31)&gt;0,OR(D31="X",D31="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F31," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C31," ",""),"0",""),"-","")))*1),0)</f>
@@ -3390,7 +3468,7 @@
         <f>RANK(U38,$U$34:$U$38)+COUNTIF($U$33:U37,U38)</f>
       </c>
       <c r="I38" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J38" s="14" t="str">
         <f>IF(OR(COUNTA(J30,K30,M30,N30)&gt;0,OR(L30="X",L30="x")),IF(OR(L30="X",L30="x",AND(OR(COUNTA(J30,K30,M30,N30)&gt;0,OR(L30="X",L30="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N30," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J30," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K30," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J31,K31,M31,N31)&gt;0,OR(L31="X",L31="x")),IF(OR(L31="X",L31="x",AND(OR(COUNTA(J31,K31,M31,N31)&gt;0,OR(L31="X",L31="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K31," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N31," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N31," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J31," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K31," ",""),"0",""),"-","")))*1),0)</f>
@@ -3420,22 +3498,22 @@
     <row r="41">
       <c r="F41" s="13"/>
       <c r="G41" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42">
       <c r="F42" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G42" s="19" t="str">
         <f>IFERROR(INDEX($A$34:$A$38, MATCH(1, $G$34:$G$38, 0)), "-")</f>
       </c>
       <c r="N42" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O42" s="19" t="str">
         <f>IFERROR(INDEX($I$34:$I$38, MATCH(1, $O$34:$O$38, 0)), "-")</f>
@@ -3443,13 +3521,13 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G43" s="19" t="str">
         <f>IFERROR(INDEX($A$34:$A$38, MATCH(2, $G$34:$G$38, 0)), "-")</f>
       </c>
       <c r="N43" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="O43" s="19" t="str">
         <f>IFERROR(INDEX($I$34:$I$38, MATCH(2, $O$34:$O$38, 0)), "-")</f>
@@ -3457,13 +3535,13 @@
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="G44" s="19" t="str">
         <f>IFERROR(INDEX($A$34:$A$38, MATCH(3, $G$34:$G$38, 0)), "-")</f>
       </c>
       <c r="N44" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="O44" s="19" t="str">
         <f>IFERROR(INDEX($I$34:$I$38, MATCH(3, $O$34:$O$38, 0)), "-")</f>
@@ -3471,13 +3549,13 @@
     </row>
     <row r="45">
       <c r="F45" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G45" s="19" t="str">
         <f>IFERROR(INDEX($A$34:$A$38, MATCH(4, $G$34:$G$38, 0)), "-")</f>
       </c>
       <c r="N45" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O45" s="19" t="str">
         <f>IFERROR(INDEX($I$34:$I$38, MATCH(4, $O$34:$O$38, 0)), "-")</f>
@@ -3485,13 +3563,13 @@
     </row>
     <row r="46">
       <c r="F46" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G46" s="19" t="str">
         <f>IFERROR(INDEX($A$34:$A$38, MATCH(5, $G$34:$G$38, 0)), "-")</f>
       </c>
       <c r="N46" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O46" s="19" t="str">
         <f>IFERROR(INDEX($I$34:$I$38, MATCH(5, $O$34:$O$38, 0)), "-")</f>
@@ -3510,18 +3588,18 @@
     </row>
     <row r="49">
       <c r="A49" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -3529,12 +3607,12 @@
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
       <c r="G50" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -3542,12 +3620,12 @@
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
       <c r="G51" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -3555,12 +3633,12 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
       <c r="G52" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -3568,35 +3646,35 @@
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
       <c r="G53" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="B56" s="14" t="str">
         <f>IF(OR(COUNTA(B50,C50,E50,F50)&gt;0,OR(D50="X",D50="x")),IF(OR(D50="X",D50="x",AND(OR(COUNTA(B50,C50,E50,F50)&gt;0,OR(D50="X",D50="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x",AND(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
@@ -3622,7 +3700,7 @@
     </row>
     <row r="57">
       <c r="A57" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B57" s="14" t="str">
         <f>IF(OR(COUNTA(B50,C50,E50,F50)&gt;0,OR(D50="X",D50="x")),IF(OR(D50="X",D50="x",AND(OR(COUNTA(B50,C50,E50,F50)&gt;0,OR(D50="X",D50="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C50," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E50," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F50," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B51,C51,E51,F51)&gt;0,OR(D51="X",D51="x")),IF(OR(D51="X",D51="x",AND(OR(COUNTA(B51,C51,E51,F51)&gt;0,OR(D51="X",D51="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-","")))*1),0)</f>
@@ -3648,7 +3726,7 @@
     </row>
     <row r="58">
       <c r="A58" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="B58" s="14" t="str">
         <f>IF(OR(COUNTA(B51,C51,E51,F51)&gt;0,OR(D51="X",D51="x")),IF(OR(D51="X",D51="x",AND(OR(COUNTA(B51,C51,E51,F51)&gt;0,OR(D51="X",D51="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F51," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B51," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C51," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x",AND(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)</f>
@@ -3674,7 +3752,7 @@
     </row>
     <row r="59">
       <c r="A59" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="B59" s="14" t="str">
         <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x",AND(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x",AND(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)</f>
@@ -3701,12 +3779,12 @@
     <row r="62">
       <c r="F62" s="13"/>
       <c r="G62" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63">
       <c r="F63" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G63" s="19" t="str">
         <f>IFERROR(INDEX($A$56:$A$59, MATCH(1, $G$56:$G$59, 0)), "-")</f>
@@ -3714,7 +3792,7 @@
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G64" s="19" t="str">
         <f>IFERROR(INDEX($A$56:$A$59, MATCH(2, $G$56:$G$59, 0)), "-")</f>
@@ -3722,7 +3800,7 @@
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="G65" s="19" t="str">
         <f>IFERROR(INDEX($A$56:$A$59, MATCH(3, $G$56:$G$59, 0)), "-")</f>
@@ -3730,7 +3808,7 @@
     </row>
     <row r="66">
       <c r="F66" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G66" s="19" t="str">
         <f>IFERROR(INDEX($A$56:$A$59, MATCH(4, $G$56:$G$59, 0)), "-")</f>
@@ -3779,7 +3857,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3788,7 +3866,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3799,7 +3877,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3810,13 +3888,13 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4">
@@ -3834,19 +3912,19 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G7" s="19"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3855,7 +3933,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="I15" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
@@ -3866,22 +3944,22 @@
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
@@ -3910,27 +3988,27 @@
     </row>
     <row r="19">
       <c r="F19" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G19" s="19"/>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O19" s="19"/>
     </row>
     <row r="20">
       <c r="F20" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G20" s="19"/>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="O20" s="19"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -3941,13 +4019,13 @@
     </row>
     <row r="29">
       <c r="A29" s="17" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30">
@@ -3965,13 +4043,13 @@
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G32" s="19"/>
     </row>
     <row r="33">
       <c r="F33" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G33" s="19"/>
     </row>
@@ -4026,12 +4104,12 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -4041,14 +4119,14 @@
     </row>
     <row r="7">
       <c r="A7" s="26" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="20"/>
     </row>
     <row r="8">
       <c r="A8" s="26" t="str">
-        <f>"4. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="G8" s="21">
         <v>2</v>
@@ -4056,7 +4134,7 @@
     </row>
     <row r="9">
       <c r="A9" s="27" t="str">
-        <f>"5. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="C9" s="23" t="str">
         <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G42)</f>
@@ -4084,27 +4162,27 @@
     </row>
     <row r="12">
       <c r="A12" s="25" t="str">
-        <f>"1. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="str">
-        <f>"2. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="str">
-        <f>"3. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="str">
-        <f>"4. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="str">
-        <f>"5. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
     </row>
     <row r="17">
@@ -4117,22 +4195,22 @@
     </row>
     <row r="19">
       <c r="A19" s="25" t="str">
-        <f>"1. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="str">
-        <f>"2. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="str">
-        <f>"3. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="str">
-        <f>"4. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
     </row>
     <row r="23">
@@ -4178,7 +4256,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool D-1st ",'Pool Matches'!O19)</f>
@@ -4186,7 +4264,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -4195,7 +4273,7 @@
     </row>
     <row r="7">
       <c r="A7" s="26" t="str">
-        <f>"3. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O42)</f>
@@ -4205,12 +4283,12 @@
     </row>
     <row r="8">
       <c r="A8" s="26" t="str">
-        <f>"4. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="27" t="str">
-        <f>"5. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="10">
@@ -4223,27 +4301,27 @@
     </row>
     <row r="12">
       <c r="A12" s="25" t="str">
-        <f>"1. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="str">
-        <f>"2. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="str">
-        <f>"3. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="str">
-        <f>"4. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="str">
-        <f>"5. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="17">

--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -25,6 +25,7 @@
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$E$17</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$14</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$10</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tags'!$A$1:$A$48</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$40</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -770,13 +771,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1746,7 +1747,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -774,7 +774,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -1512,8 +1512,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -1646,8 +1646,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-medium-seeded-one-qualifier.xlsx
+++ b/pools-example-medium-seeded-one-qualifier.xlsx
@@ -777,7 +777,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
